--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,6 +913,593 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129150506</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92811</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gubbmyran, Gubbmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>517057</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6718370</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129150462</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92847</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gubbmyran, Gubbmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>517071</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6718349</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129150830</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98651</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gubbmyran, Gubbmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516973</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6718487</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter. Ej räknade.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129150280</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98651</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gubbmyran, Gubbmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>517115</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6718208</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129150241</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98651</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gubbmyran, Gubbmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>517130</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6718211</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129011026</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129150506</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>129150462</v>
       </c>
       <c r="B5" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129150830</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>129150280</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129150241</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129011026</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129150506</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>129150462</v>
       </c>
       <c r="B5" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129150830</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>129150280</v>
       </c>
       <c r="B7" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129150241</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129011026</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129150506</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>129150462</v>
       </c>
       <c r="B5" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129150830</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>129150280</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129150241</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129011026</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129150506</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>129150462</v>
       </c>
       <c r="B5" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129150830</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>129150280</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129150241</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129011026</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129150506</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>129150462</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129150830</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>129150280</v>
       </c>
       <c r="B7" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129150241</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129011026</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129150506</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>129150462</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129150830</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>129150280</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129150241</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129011026</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129150506</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>129150462</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129150830</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>129150280</v>
       </c>
       <c r="B7" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129150241</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129011026</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129150830</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>129150280</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129150241</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129011026</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129150506</v>
       </c>
       <c r="B4" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>129150462</v>
       </c>
       <c r="B5" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129150830</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>129150280</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129150241</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129011026</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129150506</v>
       </c>
       <c r="B4" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>129150462</v>
       </c>
       <c r="B5" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129150830</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>129150280</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129150241</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129011026</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129150506</v>
       </c>
       <c r="B4" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>129150462</v>
       </c>
       <c r="B5" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129150830</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>129150280</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129150241</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129011026</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129150506</v>
       </c>
       <c r="B4" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>129150462</v>
       </c>
       <c r="B5" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129150830</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>129150280</v>
       </c>
       <c r="B7" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129150241</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129011026</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129150506</v>
       </c>
       <c r="B4" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>129150462</v>
       </c>
       <c r="B5" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129150830</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>129150280</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129150241</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>129150506</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>129150462</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129150830</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>129150280</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>129150241</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128331155</v>
+        <v>129150506</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517237</v>
+        <v>517057</v>
       </c>
       <c r="R2" t="n">
-        <v>6718324</v>
+        <v>6718370</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,73 +770,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011026</v>
+        <v>129150462</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517079</v>
+        <v>517071</v>
       </c>
       <c r="R3" t="n">
-        <v>6718455</v>
+        <v>6718349</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,29 +871,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129150506</v>
+        <v>128337675</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>8455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517057</v>
+        <v>516947</v>
       </c>
       <c r="R4" t="n">
-        <v>6718370</v>
+        <v>6718566</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,64 +980,88 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129150462</v>
+        <v>128331155</v>
       </c>
       <c r="B5" t="n">
-        <v>92899</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517071</v>
+        <v>517237</v>
       </c>
       <c r="R5" t="n">
-        <v>6718349</v>
+        <v>6718324</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,22 +1085,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,22 +1115,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129150830</v>
+        <v>129011026</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,32 +1157,34 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gubbmyran, Gubbmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516973</v>
+        <v>517079</v>
       </c>
       <c r="R6" t="n">
-        <v>6718487</v>
+        <v>6718455</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,27 +1208,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca 50 bladrosetter. Ej räknade.</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,28 +1232,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129150280</v>
+        <v>129150241</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1281,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1304,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517115</v>
+        <v>517130</v>
       </c>
       <c r="R7" t="n">
-        <v>6718208</v>
+        <v>6718211</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129150241</v>
+        <v>129150280</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1407,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1425,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517130</v>
+        <v>517115</v>
       </c>
       <c r="R8" t="n">
-        <v>6718211</v>
+        <v>6718208</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,6 +1495,132 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129150830</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gubbmyran, Gubbmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>516973</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6718487</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 50 bladrosetter. Ej räknade.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49835-2025 artfynd.xlsx
+++ b/artfynd/A 49835-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150506</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150462</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128337675</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128331155</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1248,6 +1273,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150241</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1495,6 +1530,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150280</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1621,8 +1661,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150830</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>